--- a/public/exports/35209115.xlsx
+++ b/public/exports/35209115.xlsx
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033966</t>
+          <t xml:space="preserve">311033953</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">

--- a/public/exports/35209115.xlsx
+++ b/public/exports/35209115.xlsx
@@ -5694,7 +5694,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013008</t>
+          <t xml:space="preserve">310013009</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013008</t>
+          <t xml:space="preserve">310013009</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311025697</t>
+          <t xml:space="preserve">311025709</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843433</t>
+          <t xml:space="preserve">311843436</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843432</t>
+          <t xml:space="preserve">311843431</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843432</t>
+          <t xml:space="preserve">311843431</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864275</t>
+          <t xml:space="preserve">311864280</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873922</t>
+          <t xml:space="preserve">311873923</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873922</t>
+          <t xml:space="preserve">311873923</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873941</t>
+          <t xml:space="preserve">311873939</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899990</t>
+          <t xml:space="preserve">311899994</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311903990</t>
+          <t xml:space="preserve">311903989</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907591</t>
+          <t xml:space="preserve">311907589</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908679</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908688</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908683</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -27054,7 +27054,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912852</t>
+          <t xml:space="preserve">311912853</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912852</t>
+          <t xml:space="preserve">311912853</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923077</t>
+          <t xml:space="preserve">311923076</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923077</t>
+          <t xml:space="preserve">311923076</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -28254,7 +28254,7 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923054</t>
+          <t xml:space="preserve">311923056</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -28314,7 +28314,7 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923055</t>
+          <t xml:space="preserve">311923056</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923007</t>
+          <t xml:space="preserve">311922996</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923008</t>
+          <t xml:space="preserve">311922996</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923219</t>
+          <t xml:space="preserve">311923222</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923219</t>
+          <t xml:space="preserve">311923222</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923219</t>
+          <t xml:space="preserve">311923222</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -29214,7 +29214,7 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923219</t>
+          <t xml:space="preserve">311923222</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">

--- a/public/exports/35209115.xlsx
+++ b/public/exports/35209115.xlsx
@@ -6164,12 +6164,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013009</t>
+          <t xml:space="preserve">310013008</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013009</t>
+          <t xml:space="preserve">310013008</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">TRE-FOR Energi A/S</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311025709</t>
+          <t xml:space="preserve">311025697</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033966</t>
+          <t xml:space="preserve">311033953</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843432</t>
+          <t xml:space="preserve">311843431</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843432</t>
+          <t xml:space="preserve">311843431</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864279</t>
+          <t xml:space="preserve">311864275</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -15719,12 +15719,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873923</t>
+          <t xml:space="preserve">311873922</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873923</t>
+          <t xml:space="preserve">311873922</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908688</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -23714,7 +23714,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908683</t>
+          <t xml:space="preserve">311908678</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -29889,7 +29889,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923048</t>
+          <t xml:space="preserve">311923044</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923048</t>
+          <t xml:space="preserve">311923045</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923088</t>
+          <t xml:space="preserve">311923085</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -30799,12 +30799,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923007</t>
+          <t xml:space="preserve">311922996</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -30864,12 +30864,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923008</t>
+          <t xml:space="preserve">311922996</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K475" t="inlineStr">
